--- a/data/trans_orig/P1426-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2012</t>
+          <t>Población con diagnóstico de hipoacusia en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42155</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59595</t>
+          <t>59279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57017</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93533</t>
+          <t>95269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>932488</t>
+          <t>931367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>955610</t>
+          <t>954635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1278202</t>
+          <t>1278518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1305435</t>
+          <t>1305927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2218907</t>
+          <t>2217171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2255423</t>
+          <t>2253730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1936254</t>
+          <t>1936280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1953227</t>
+          <t>1953133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1729731</t>
+          <t>1728180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1746455</t>
+          <t>1745635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3671348</t>
+          <t>3671813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3695888</t>
+          <t>3695963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20877</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466919</t>
+          <t>466200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480127</t>
+          <t>480134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445975</t>
+          <t>445185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456492</t>
+          <t>456443</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>918936</t>
+          <t>918979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934545</t>
+          <t>934647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>40575</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69798</t>
+          <t>70700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50534</t>
+          <t>51814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82766</t>
+          <t>83619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97329</t>
+          <t>95776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142359</t>
+          <t>140773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3349984</t>
+          <t>3349082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3380286</t>
+          <t>3379207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3468254</t>
+          <t>3467401</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3500486</t>
+          <t>3499206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6828442</t>
+          <t>6830028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6873472</t>
+          <t>6875025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2016</t>
+          <t>Población con diagnóstico de hipoacusia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34517</t>
+          <t>34600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>26529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49208</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80255</t>
+          <t>76022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>719830</t>
+          <t>719747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>738732</t>
+          <t>738084</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>945452</t>
+          <t>944697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>969820</t>
+          <t>968131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1668752</t>
+          <t>1672985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1701536</t>
+          <t>1703275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,77 +2698,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>26971</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17459</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>38984</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>47057</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>34727</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>63270</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26971</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17609</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>39395</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>47057</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>34203</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>63971</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2043936</t>
+          <t>2043601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2063919</t>
+          <t>2063923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,82 +2806,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1961329</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1949316</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1970841</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4017628</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4001415</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4029958</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>98,44%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1961329</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1948905</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1970691</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4017628</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4000714</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4030482</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>22957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535317</t>
+          <t>535044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545307</t>
+          <t>545313</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532711</t>
+          <t>532804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545814</t>
+          <t>545263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1071701</t>
+          <t>1073070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089176</t>
+          <t>1089101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65418</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55076</t>
+          <t>55441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90281</t>
+          <t>88173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98574</t>
+          <t>99578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143148</t>
+          <t>144158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3312200</t>
+          <t>3314639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3340747</t>
+          <t>3341013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3441819</t>
+          <t>3443927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3477024</t>
+          <t>3476659</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6766570</t>
+          <t>6765560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6811144</t>
+          <t>6810140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2023</t>
+          <t>Población con diagnóstico de hipoacusia en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49425</t>
+          <t>49044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72252</t>
+          <t>72361</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80592</t>
+          <t>80915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106803</t>
+          <t>107027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136535</t>
+          <t>135100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171198</t>
+          <t>170154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441690</t>
+          <t>441581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464517</t>
+          <t>464898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>645766</t>
+          <t>645542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671977</t>
+          <t>671654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1095313</t>
+          <t>1096357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1129976</t>
+          <t>1131411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>49099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88609</t>
+          <t>88612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,82 +4296,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>49597</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35174</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62607</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>120290</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>92838</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>145122</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>49597</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>34051</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>63028</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>120290</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>93690</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>141256</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2199828</t>
+          <t>2199825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2241485</t>
+          <t>2239338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4414,77 +4414,77 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2186088</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2173078</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2200511</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4403831</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4378999</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4431283</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>97,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2186088</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2172657</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2201634</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4717</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4403831</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4382865</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4430431</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32936</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23892</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613687</t>
+          <t>612303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631190</t>
+          <t>630110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635779</t>
+          <t>635578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647779</t>
+          <t>647829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255153</t>
+          <t>1255042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1276121</t>
+          <t>1275857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>119926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176765</t>
+          <t>179156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130654</t>
+          <t>131087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182644</t>
+          <t>180339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267432</t>
+          <t>267054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348100</t>
+          <t>346222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3272237</t>
+          <t>3269846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3331244</t>
+          <t>3329076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3465280</t>
+          <t>3467585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3517270</t>
+          <t>3516837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6748826</t>
+          <t>6750704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6829494</t>
+          <t>6829872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1426-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43276</t>
+          <t>43189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59279</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58710</t>
+          <t>57635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95269</t>
+          <t>94335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>931367</t>
+          <t>931454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>954635</t>
+          <t>954387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1278518</t>
+          <t>1278639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1305927</t>
+          <t>1305685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2217171</t>
+          <t>2218105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2253730</t>
+          <t>2254805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27677</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>46481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1936280</t>
+          <t>1935105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1953133</t>
+          <t>1953218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1728180</t>
+          <t>1729276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1745635</t>
+          <t>1746323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3671813</t>
+          <t>3672068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3695963</t>
+          <t>3696274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>14613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466200</t>
+          <t>466568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480134</t>
+          <t>480131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445185</t>
+          <t>445251</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456443</t>
+          <t>456413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>918979</t>
+          <t>917533</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934647</t>
+          <t>934639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70700</t>
+          <t>70745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51814</t>
+          <t>50949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83619</t>
+          <t>84039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95776</t>
+          <t>98309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140773</t>
+          <t>141845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3349082</t>
+          <t>3349037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3379207</t>
+          <t>3380229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3467401</t>
+          <t>3466981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3499206</t>
+          <t>3500071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6830028</t>
+          <t>6828956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6875025</t>
+          <t>6872492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>35402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76022</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>719747</t>
+          <t>718945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>738084</t>
+          <t>737619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>944697</t>
+          <t>945645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>968131</t>
+          <t>968655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1672985</t>
+          <t>1672118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1703275</t>
+          <t>1701909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>32806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38984</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>34360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63270</t>
+          <t>61976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2043601</t>
+          <t>2043579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2063923</t>
+          <t>2063813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1949316</t>
+          <t>1947712</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1970841</t>
+          <t>1970192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4001415</t>
+          <t>4002709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4029958</t>
+          <t>4030325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535044</t>
+          <t>534191</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545313</t>
+          <t>545316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532804</t>
+          <t>532758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545263</t>
+          <t>545919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073070</t>
+          <t>1073555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089101</t>
+          <t>1089652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36605</t>
+          <t>35617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62979</t>
+          <t>63506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>55560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88173</t>
+          <t>91908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99578</t>
+          <t>99043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144158</t>
+          <t>142739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3314639</t>
+          <t>3314112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3341013</t>
+          <t>3342001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3443927</t>
+          <t>3440192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3476659</t>
+          <t>3476540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6765560</t>
+          <t>6766979</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6810140</t>
+          <t>6810675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59830</t>
+          <t>62258</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49044</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72361</t>
+          <t>75766</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>100767</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80915</t>
+          <t>87772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107027</t>
+          <t>115777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>153085</t>
+          <t>163025</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135100</t>
+          <t>145479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170154</t>
+          <t>182974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>454112</t>
+          <t>515284</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441581</t>
+          <t>501776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464898</t>
+          <t>525276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>659314</t>
+          <t>719933</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>645542</t>
+          <t>704923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671654</t>
+          <t>732928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1113426</t>
+          <t>1235217</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1096357</t>
+          <t>1215268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1131411</t>
+          <t>1252763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752569</t>
+          <t>820700</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752569</t>
+          <t>820700</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752569</t>
+          <t>820700</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266511</t>
+          <t>1398242</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266511</t>
+          <t>1398242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266511</t>
+          <t>1398242</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>75995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>61402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88612</t>
+          <t>91380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49597</t>
+          <t>52966</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>65765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>120290</t>
+          <t>128961</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>112007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145122</t>
+          <t>151797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2217744</t>
+          <t>2152535</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2199825</t>
+          <t>2137150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2239338</t>
+          <t>2167128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2186088</t>
+          <t>2115724</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2173078</t>
+          <t>2102925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2200511</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4403831</t>
+          <t>4268259</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4378999</t>
+          <t>4245423</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4431283</t>
+          <t>4285213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288437</t>
+          <t>2228530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288437</t>
+          <t>2228530</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288437</t>
+          <t>2228530</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235685</t>
+          <t>2168690</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235685</t>
+          <t>2168690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235685</t>
+          <t>2168690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524121</t>
+          <t>4397220</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524121</t>
+          <t>4397220</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524121</t>
+          <t>4397220</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>36847</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39787</t>
+          <t>45271</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>57702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>623630</t>
+          <t>686398</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612303</t>
+          <t>674740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630110</t>
+          <t>694982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>642877</t>
+          <t>713957</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635578</t>
+          <t>706772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647829</t>
+          <t>719903</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1266507</t>
+          <t>1400355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255042</t>
+          <t>1387924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275857</t>
+          <t>1410713</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659671</t>
+          <t>734039</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659671</t>
+          <t>734039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659671</t>
+          <t>734039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306294</t>
+          <t>1445626</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306294</t>
+          <t>1445626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306294</t>
+          <t>1445626</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>153516</t>
+          <t>163442</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119926</t>
+          <t>143652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179156</t>
+          <t>187415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>159646</t>
+          <t>173815</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131087</t>
+          <t>154104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180339</t>
+          <t>194490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>313163</t>
+          <t>337258</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267054</t>
+          <t>309241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>346222</t>
+          <t>369644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3295486</t>
+          <t>3354217</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3269846</t>
+          <t>3330244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3329076</t>
+          <t>3374007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3488278</t>
+          <t>3549613</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3467585</t>
+          <t>3528938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3516837</t>
+          <t>3569324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6783763</t>
+          <t>6903829</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6750704</t>
+          <t>6871443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6829872</t>
+          <t>6931846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449002</t>
+          <t>3517659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449002</t>
+          <t>3517659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449002</t>
+          <t>3517659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647924</t>
+          <t>3723428</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647924</t>
+          <t>3723428</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647924</t>
+          <t>3723428</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7096926</t>
+          <t>7241087</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7096926</t>
+          <t>7241087</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7096926</t>
+          <t>7241087</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
